--- a/admin/company-flow-server/crew_registry/ops.persona_generate/1.0.0/output/TestQA.xlsx
+++ b/admin/company-flow-server/crew_registry/ops.persona_generate/1.0.0/output/TestQA.xlsx
@@ -483,95 +483,91 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>JiraScenarioExtractionTask</t>
+          <t>ExtractTestScenarios</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Jira 시스템에서 테스트 케이스 및 관련 정보를 추출하여, 시나리오 대로 완벽히 테스트가 가능한지 확인하기 위한 기초 데이터를 확보합니다.</t>
+          <t>테스트 시나리오를 추출하고, 필요한 모든 정보를 수집합니다.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Jira에서 추출된 테스트 시나리오 목록과 각 시나리오의 상세 내용이 명확하게 정리된 문서.</t>
+          <t>정의된 테스트 시나리오 목록과 각 시나리오에 필요한 데이터 및 환경 설정 정보</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>extracted_jira_scenarios.md</t>
+          <t>extracted_test_scenarios.json</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>JiraScenarioExtractor</t>
+          <t>ScenarioExtractorAgent</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Jira 시스템에 접속하여 테스트 케이스, 요구사항, 관련 이슈 등 테스트 시나리오 검증에 필요한 모든 정보를 정확하게 추출하는 전문가.</t>
+          <t>테스트 시나리오 추출자</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Jira에 등록된 테스트 시나리오와 연관된 모든 정보를 빠짐없이 추출하여, 다음 분석 단계에 필요한 정확하고 완전한 데이터를 제공합니다.</t>
+          <t>주어진 요구사항 및 프로그램을 기반으로 효과적인 테스트 시나리오를 정확하게 식별하고 추출하는 것</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>수년간 Jira를 활용하여 다양한 프로젝트의 테스트 정보를 관리하고 추출해온 경험을 바탕으로, 복잡한 Jira 구조 속에서 필요한 테스트 시나리오 데이터를 효율적이고 정확하게 찾아내는 데 특화된 베테랑입니다.</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>jira.get_issue</t>
-        </is>
-      </c>
+          <t>수년간의 테스트 경험을 바탕으로, 복잡한 시스템의 숨겨진 시나리오까지 찾아내는 전문가입니다. 모든 가능한 테스트 경로를 고려하여 완벽한 시나리오를 구성합니다.</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>TestScenarioAnalysisTask</t>
+          <t>AnalyzeTestResults</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>JiraScenarioExtractionTask</t>
+          <t>ExtractTestScenarios</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>이전 단계에서 추출된 Jira 테스트 시나리오 데이터를 기반으로, 시나리오의 완결성, 정확성, 그리고 실제 테스트 적용 가능성을 심층적으로 분석하여, 완벽한 테스트 수행 여부를 판단합니다.</t>
+          <t>추출된 테스트 시나리오를 분석하고, 테스트 결과를 평가합니다.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>각 테스트 시나리오의 분석 결과, 잠재적 문제점, 개선 제안, 그리고 완벽한 테스트 수행 가능성에 대한 종합적인 판단이 포함된 상세 분석 보고서.</t>
+          <t>테스트 시나리오 분석 보고서, 잠재적 결함 또는 개선 사항 목록</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>test_scenario_analysis_report.md</t>
+          <t>test_analysis_report.md</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>ScenarioAnalyst</t>
+          <t>TestAnalyzerAgent</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>추출된 테스트 시나리오와 비즈니스 요구사항을 비교 분석하여 시나리오의 결함을 식별하고, 실제 테스트 실행 시 발생할 수 있는 잠재적 문제를 예측하는 고도화된 분석가.</t>
+          <t>테스트 결과 분석가</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>주어진 테스트 시나리오가 비즈니스 목표와 프로그램 개발의 품질 기준에 따라 완벽하게 테스트될 수 있는지 여부를 종합적으로 판단하고, 근거 있는 분석 결과를 도출합니다.</t>
+          <t>수집된 테스트 데이터를 심층적으로 분석하여 시스템의 잠재적 문제점과 개선 기회를 파악하는 것</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>수많은 프로그램 개발 프로젝트에서 복잡한 테스트 시나리오를 분석하고 개선해 온 경험을 보유하고 있으며, 정교한 분석 기술과 비판적 사고를 통해 테스트의 품질을 한 단계 끌어올리는 데 기여해 왔습니다.</t>
+          <t>데이터 분석 및 품질 보증 분야에서 탁월한 능력을 발휘하며, 통계적 방법과 논리적 추론을 통해 테스트 결과의 깊은 의미를 이해합니다. 시스템 품질 향상에 기여하는 것이 그의 최우선 목표입니다.</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
